--- a/stories/arbres/ATOM-SOC.TRA.002-07.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Étienne monte dans la voiture. Papa est l'adulte. Étienne pose ses fesses. Il est assis. Son dos est contre le siège. Ses pieds sont sur le tapis. Ses mains tiennent le doudou. Papa dit : on reste assis. Avec l'adulte. La voiture roule. Étienne reste assis. Papa est là. Ils arrivent. Étienne reste assis. Papa défait la ceinture. Étienne donne la main.</t>
+          <t>Étienne monte dans la voiture. Papa est l'adulte. Étienne pose ses fesses. Il est assis. Son dos est contre le siège. Ses pieds sont sur le tapis. Ses mains tiennent le doudou. On reste assis. Avec l'adulte. La voiture roule. Étienne reste assis. Papa est là. Ils arrivent. Étienne reste assis. Papa défait la ceinture. Étienne donne la main.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne monte dans la voiture. Papa est l'adulte. Étienne pose ses fesses. Il est assis. Son dos est contre le siège. Ses pieds sont sur le tapis. Ses mains tiennent le doudou.
+papa|On reste assis. Avec l'adulte.
+narrateur|La voiture roule. Étienne reste assis. Papa est là. Ils arrivent. Étienne reste assis. Papa défait la ceinture. Étienne donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne est dans la voiture. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne est resté assis. Ses fesses étaient sur le siège. Papa, l'adulte, était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne tient la main de papa. Ils vont vers la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-07.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|La voiture roule. Étienne reste assis. Papa est là. Ils arrivent. Étienne reste assis. Papa défait la ceinture. Étienne donne la main.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Étienne est dans la voiture. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Étienne est resté assis. Ses fesses étaient sur le siège. Papa, l'adulte, était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Étienne tient la main de papa. Ils vont vers la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.002-07.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Étienne reste assis dans la voiture</t>
+          <t>La gourde de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut le gâteau rond pour mamie. La gourde tombe. Papa la pose. Mila reste assise. Ils ouvrent la boîte au village.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Étienne monte dans la voiture. Papa est l'adulte. Étienne pose ses fesses. Il est assis. Son dos est contre le siège. Ses pieds sont sur le tapis. Ses mains tiennent le doudou. On reste assis. Avec l'adulte. La voiture roule. Étienne reste assis. Papa est là. Ils arrivent. Étienne reste assis. Papa défait la ceinture. Étienne donne la main.</t>
+          <t>La boîte à gâteaux sent encore le beurre. Elle est sur le siège, à côté. Le parking sent l'asphalte chaud. Une cigale chante dans un platane. Tu as senti les gâteaux, Mila ? Ça sent le beurre. Oui. On les porte à mamie. Je veux le gâteau rond. Il est dans la boîte. On l'ouvrira là bas. En ce moment, Mila est sur le siège. Papa attache la ceinture, clic. La gourde bleue est dans le filet. Ses pieds touchent le tapis. On reste assis, avec l'adulte. Tu restes assise, d'accord ? D'accord. La voiture part tout doux. Les platanes défilent, gris. Mila regarde la boîte. Il est où, le rond ? Dans la boîte, tout au fond. Un virage penche un peu. La gourde tombe sur le tapis. Elle fait un bruit mou. Ma gourde ! Mila tend la main. La ceinture la retient, douce. Je la prends. Toi, tu restes assise. Papa pose la gourde dans le filet. Mila reste assise. Elle est revenue. Oui. Tes fesses n'ont pas bougé. Merci, Mila. Les platanes font de l'ombre, puis du soleil. La cigale se perd, loin. On arrive bientôt ? Après le pont. Le pont fait un petit bruit de fer. Mila tient la boîte d'un doigt. Doucement. Elle reste assise. Un camion passe, tout bruyant. La boîte tremble, puis tient. Les gâteaux aussi. Oui. Toi aussi, tu tiens.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Étienne monte dans la voiture. Papa est l'adulte. Étienne pose ses fesses. Il est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Son dos est contre le siège. Ses pieds sont sur le tapis. Ses mains tiennent le doudou. Papa dit : on reste assis. Avec l'adulte. La voiture roule. Étienne reste assis. Papa est là. Ils arrivent. Étienne reste assis. Papa défait la ceinture. Étienne donne la main.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La boîte à gâteaux sent encore le beurre. Elle est sur le siège, à côté. Le parking sent l'asphalte chaud. Une cigale chante dans un platane. Tu as senti les gâteaux, Mila ? Ça sent le beurre. Oui. On les porte à mamie. Je veux le gâteau rond. Il est dans la boîte. On l'ouvrira là bas. En ce moment, Mila est sur le siège. Papa attache la ceinture, clic. La gourde bleue est dans le filet. Ses pieds touchent le tapis. On reste assis, avec l'adulte. Tu restes assise, d'accord ? D'accord. La voiture part tout doux. Les platanes défilent, gris. Mila regarde la boîte. Il est où, le rond ? Dans la boîte, tout au fond. Un virage penche un peu. La gourde tombe sur le tapis. Elle fait un bruit mou. Ma gourde ! Mila tend la main. La ceinture la retient, douce. Je la prends. Toi, tu restes assise. Papa pose la gourde dans le filet. Mila reste assise. Elle est revenue. Oui. Tes fesses n'ont pas bougé. Merci, Mila. Les platanes font de l'ombre, puis du soleil. La cigale se perd, loin. On arrive bientôt ? Après le pont. Le pont fait un petit bruit de fer. Mila tient la boîte d'un doigt. Doucement. Elle reste assise. Un camion passe, tout bruyant. La boîte tremble, puis tient. Les gâteaux aussi. Oui. Toi aussi, tu tiens.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Étienne monte dans la voiture. Papa est l'adulte. Étienne pose ses fesses. Il est assis. Son dos est contre le siège. Ses pieds sont sur le tapis. Ses mains tiennent le doudou.
-papa|On reste assis. Avec l'adulte.
-narrateur|La voiture roule. Étienne reste assis. Papa est là. Ils arrivent. Étienne reste assis. Papa défait la ceinture. Étienne donne la main.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La boîte à gâteaux sent encore le beurre.
+narrateur|Elle est sur le siège, à côté.
+narrateur|Le parking sent l'asphalte chaud.
+narrateur|Une cigale chante dans un platane.
+papa|Tu as senti les gâteaux, Mila ?
+enfant-f|Ça sent le beurre.
+papa|Oui.
+papa|On les porte à mamie.
+enfant-f|Je veux le gâteau rond.
+papa|Il est dans la boîte.
+papa|On l'ouvrira là bas.
+narrateur|En ce moment, Mila est sur le siège.
+narrateur|Papa attache la ceinture, clic.
+narrateur|La gourde bleue est dans le filet.
+narrateur|Ses pieds touchent le tapis.
+papa|On reste assis, avec l'adulte.
+papa|Tu restes assise, d'accord ?
+enfant-f|D'accord.
+narrateur|La voiture part tout doux.
+narrateur|Les platanes défilent, gris.
+narrateur|Mila regarde la boîte.
+enfant-f|Il est où, le rond ?
+papa|Dans la boîte, tout au fond.
+narrateur|Un virage penche un peu.
+narrateur|La gourde tombe sur le tapis.
+narrateur|Elle fait un bruit mou.
+enfant-f|Ma gourde !
+narrateur|Mila tend la main.
+narrateur|La ceinture la retient, douce.
+papa|Je la prends.
+papa|Toi, tu restes assise.
+narrateur|Papa pose la gourde dans le filet.
+narrateur|Mila reste assise.
+enfant-f|Elle est revenue.
+papa|Oui.
+papa|Tes fesses n'ont pas bougé.
+papa|Merci, Mila.
+narrateur|Les platanes font de l'ombre, puis du soleil.
+narrateur|La cigale se perd, loin.
+enfant-f|On arrive bientôt ?
+papa|Après le pont.
+narrateur|Le pont fait un petit bruit de fer.
+narrateur|Mila tient la boîte d'un doigt.
+papa|Doucement.
+narrateur|Elle reste assise.
+narrateur|Un camion passe, tout bruyant.
+narrateur|La boîte tremble, puis tient.
+enfant-f|Les gâteaux aussi.
+papa|Oui.
+papa|Toi aussi, tu tiens.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>voiture</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,12 +1405,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Étienne est dans la voiture. Que fait-il ?</t>
+          <t>Mila est dans la voiture. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Étienne est dans la voiture. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est dans la voiture. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1362,7 +1425,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>assis | rester assis | avec papa | avec l'adulte</t>
+          <t>assis | assise | rester assise | elle reste assise | avec papa | avec l'adulte</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1377,7 +1440,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ses fesses sont sur le siège. Que fait Étienne ?</t>
+          <t>La gourde est tombée. Mila est restée où ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1426,7 +1489,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1565,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Étienne est dans la voiture. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila est dans la voiture.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Étienne est resté assis. Ses fesses étaient sur le siège. Papa, l'adulte, était là.</t>
+          <t>Mila est restée assise. La gourde est revenue dans le filet. Tes fesses étaient sur le siège. Bravo. J'ai pas bougé. Oui. On sort quand je le dis. Le village arrive, petit. Les volets sont verts. Mamie ? Tout près. Mila serre la boîte. Elle reste assise. La gourde ne bouge plus. Tu la vois, dans le filet ? Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Étienne est resté &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Ses fesses étaient sur le siège. Papa, l'adulte, était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est restée assise. La gourde est revenue dans le filet. Tes fesses étaient sur le siège. Bravo. J'ai pas bougé. Oui. On sort quand je le dis. Le village arrive, petit. Les volets sont verts. Mamie ? Tout près. Mila serre la boîte. Elle reste assise. La gourde ne bouge plus. Tu la vois, dans le filet ? Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1591,14 +1654,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1741,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Étienne est resté assis. Ses fesses étaient sur le siège. Papa, l'adulte, était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila est restée assise.
+narrateur|La gourde est revenue dans le filet.
+papa|Tes fesses étaient sur le siège.
+papa|Bravo.
+enfant-f|J'ai pas bougé.
+papa|Oui.
+papa|On sort quand je le dis.
+narrateur|Le village arrive, petit.
+narrateur|Les volets sont verts.
+enfant-f|Mamie ?
+papa|Tout près.
+narrateur|Mila serre la boîte.
+narrateur|Elle reste assise.
+narrateur|La gourde ne bouge plus.
+papa|Tu la vois, dans le filet ?
+enfant-f|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Étienne tient la main de papa. Ils vont vers la maison.</t>
+          <t>La voiture s'arrête. Le bitume sent encore le chaud. Maintenant on sort. Tu me donnes la main ? Oui, papa. Papa défait la ceinture. Mila descend, la boîte contre elle. Papa prend la gourde bleue. Elle est rentrée. Oui. Toi, tu es restée assise. La porte de mamie claque doucement. Ça sent le café, dedans. Le gâteau rond. On l'ouvre ensemble.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Étienne tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils vont vers la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture s'arrête. Le bitume sent encore le chaud. Maintenant on sort. Tu me donnes la main ? Oui, papa. Papa défait la ceinture. Mila descend, la boîte contre elle. Papa prend la gourde bleue. Elle est rentrée. Oui. Toi, tu es restée assise. La porte de mamie claque doucement. Ça sent le café, dedans. Le gâteau rond. On l'ouvre ensemble.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,14 +1844,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1850,10 +1927,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Étienne tient la main de papa. Ils vont vers la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La voiture s'arrête.
+narrateur|Le bitume sent encore le chaud.
+papa|Maintenant on sort.
+papa|Tu me donnes la main ?
+enfant-f|Oui, papa.
+narrateur|Papa défait la ceinture.
+narrateur|Mila descend, la boîte contre elle.
+narrateur|Papa prend la gourde bleue.
+enfant-f|Elle est rentrée.
+papa|Oui.
+papa|Toi, tu es restée assise.
+narrateur|La porte de mamie claque doucement.
+narrateur|Ça sent le café, dedans.
+enfant-f|Le gâteau rond.
+papa|On l'ouvre ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,12 +1968,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila pose la boîte sur la table. Le gâteau rond est encore un peu chaud. Il est là. Oui. Tu l'as porté, assise. La gourde bleue attend près du pain. Le beurre sent encore, tout près.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila pose la boîte sur la table. Le gâteau rond est encore un peu chaud. Il est là. Oui. Tu l'as porté, assise. La gourde bleue attend près du pain. Le beurre sent encore, tout près.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,14 +2029,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2108,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Mila pose la boîte sur la table.
+narrateur|Le gâteau rond est encore un peu chaud.
+enfant-f|Il est là.
+papa|Oui.
+papa|Tu l'as porté, assise.
+narrateur|La gourde bleue attend près du pain.
+narrateur|Le beurre sent encore, tout près.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2173,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-07.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>voiture</t>
+          <t>voiture, route vers le village</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Étienne, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
